--- a/data/trans_orig/IP26C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP26C-Edad-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99732</t>
+          <t>99945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218477</t>
+          <t>218576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>235262</t>
+          <t>234897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246275</t>
+          <t>245695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233604</t>
+          <t>233883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244980</t>
+          <t>245091</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>473587</t>
+          <t>473312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>488698</t>
+          <t>488512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14402</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105895</t>
+          <t>105225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117366</t>
+          <t>117081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121956</t>
+          <t>122085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133062</t>
+          <t>133003</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>231813</t>
+          <t>231522</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>247944</t>
+          <t>247330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>36295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132413</t>
+          <t>132674</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152884</t>
+          <t>152288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152364</t>
+          <t>152153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170228</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>291442</t>
+          <t>290940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319010</t>
+          <t>318303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,96%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38733</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57991</t>
+          <t>59074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49063</t>
+          <t>49402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75123</t>
+          <t>75948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101639</t>
+          <t>102599</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>586422</t>
+          <t>586184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>613781</t>
+          <t>613347</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>635695</t>
+          <t>634475</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>660419</t>
+          <t>661154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1229862</t>
+          <t>1230886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1268979</t>
+          <t>1268681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61995</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89184</t>
+          <t>88973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50902</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74007</t>
+          <t>75421</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>116898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155285</t>
+          <t>153956</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16413</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136962</t>
+          <t>136454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141835</t>
+          <t>141831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131771</t>
+          <t>133076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139687</t>
+          <t>139785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272161</t>
+          <t>271824</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>280829</t>
+          <t>280754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>215216</t>
+          <t>214217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226437</t>
+          <t>226103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246907</t>
+          <t>246377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258308</t>
+          <t>257921</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464769</t>
+          <t>464998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>481546</t>
+          <t>481682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34444</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130579</t>
+          <t>130445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143822</t>
+          <t>144205</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132117</t>
+          <t>132231</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145045</t>
+          <t>145555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>266245</t>
+          <t>267811</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>285787</t>
+          <t>286477</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>24503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>44777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120700</t>
+          <t>120099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139018</t>
+          <t>139119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125084</t>
+          <t>123884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142922</t>
+          <t>143501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250838</t>
+          <t>251739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277543</t>
+          <t>277502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30121</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49166</t>
+          <t>48843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48978</t>
+          <t>49882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66192</t>
+          <t>66116</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91728</t>
+          <t>92440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>641650</t>
+          <t>641884</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>648913</t>
+          <t>648420</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>676986</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1274500</t>
+          <t>1274265</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1314192</t>
+          <t>1312906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82091</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60985</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88626</t>
+          <t>87046</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123829</t>
+          <t>124798</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160296</t>
+          <t>161856</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120631</t>
+          <t>120411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125501</t>
+          <t>125414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114129</t>
+          <t>113213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237235</t>
+          <t>237017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243365</t>
+          <t>243409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>449</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191400</t>
+          <t>191351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202673</t>
+          <t>201982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>234953</t>
+          <t>234598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247505</t>
+          <t>247585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>430290</t>
+          <t>431159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447276</t>
+          <t>447670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34393</t>
+          <t>32885</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>155711</t>
+          <t>155153</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>170283</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157846</t>
+          <t>157907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>172508</t>
+          <t>172281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>317704</t>
+          <t>318221</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>339408</t>
+          <t>339979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>32227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>29126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35617</t>
+          <t>35671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57561</t>
+          <t>56590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137311</t>
+          <t>137958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152754</t>
+          <t>153308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135027</t>
+          <t>136085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151444</t>
+          <t>152199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>276855</t>
+          <t>277484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300693</t>
+          <t>301375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31820</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20402</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41866</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63959</t>
+          <t>63042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>618748</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>643296</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>682042</t>
+          <t>683063</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1282914</t>
+          <t>1283267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1318549</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70655</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79651</t>
+          <t>78598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>108232</t>
+          <t>108170</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>142180</t>
+          <t>142307</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49128</t>
+          <t>49109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55311</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54361</t>
+          <t>54269</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59468</t>
+          <t>59304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106564</t>
+          <t>106116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113905</t>
+          <t>113740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140483</t>
+          <t>140262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151301</t>
+          <t>151735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160646</t>
+          <t>160054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172933</t>
+          <t>173051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304832</t>
+          <t>306684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>321826</t>
+          <t>322184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>32426</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147537</t>
+          <t>147026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161283</t>
+          <t>160452</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169344</t>
+          <t>168889</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>188859</t>
+          <t>189034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>321768</t>
+          <t>321644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>345300</t>
+          <t>346666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25520</t>
+          <t>25946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22731</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>42596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39104</t>
+          <t>38265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>62876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>239670</t>
+          <t>239504</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>258158</t>
+          <t>257672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>261731</t>
+          <t>262833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283033</t>
+          <t>283311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>507731</t>
+          <t>506122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>536487</t>
+          <t>534790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33324</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41236</t>
+          <t>42837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69669</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>468</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>590105</t>
+          <t>590672</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>616482</t>
+          <t>616500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>662807</t>
+          <t>662358</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>694049</t>
+          <t>694501</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1259418</t>
+          <t>1259823</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1301361</t>
+          <t>1302153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>43925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69011</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61217</t>
+          <t>62606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93255</t>
+          <t>94050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114326</t>
+          <t>115061</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155101</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
